--- a/bin/Release/net8.0/Files/Prabhat Panel Chart.xlsx
+++ b/bin/Release/net8.0/Files/Prabhat Panel Chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$464</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$465</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2432,6 +2432,9 @@
   </x:si>
   <x:si>
     <x:t>17/08/2026 to 22/08/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24/08/2026 to 29/08/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -2887,7 +2890,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V464"/>
+  <x:dimension ref="A1:V465"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -34419,22 +34422,22 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="N464" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="O464" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="P464" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="Q464" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="R464" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="S464" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="T464" s="3" t="s">
         <x:v>41</x:v>
@@ -34446,8 +34449,76 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="465" spans="1:22">
+      <x:c r="A465" s="3" t="s">
+        <x:v>805</x:v>
+      </x:c>
+      <x:c r="B465" s="3" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="C465" s="3" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D465" s="3" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="E465" s="3" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="F465" s="3" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G465" s="3" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="H465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V465" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V464"/>
+  <x:autoFilter ref="A1:V465"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -34470,39 +34541,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>805</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>806</x:v>
+        <x:v>807</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>807</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>808</x:v>
+        <x:v>809</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>809</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>810</x:v>
+        <x:v>811</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>811</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>463</x:v>
+        <x:v>464</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>812</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -34510,10 +34581,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>813</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>804</x:v>
+        <x:v>805</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
